--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487842_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487842_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8165</v>
+        <v>3.8627</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6962</v>
+        <v>3.6543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1203</v>
+        <v>0.2083</v>
       </c>
       <c r="G2" t="n">
         <v>0.8331</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1404</v>
+        <v>-1.0943</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5252</v>
+        <v>-0.5672</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6152</v>
+        <v>-0.5271</v>
       </c>
       <c r="V2" t="n">
         <v>2.4589</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2309</v>
+        <v>-0.3608</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0064</v>
+        <v>-1.0483</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7755</v>
+        <v>0.6875</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7284</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3973</v>
+        <v>-0.5273</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1338</v>
+        <v>-0.1757</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2635</v>
+        <v>-0.3516</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3538</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7876</v>
+        <v>-0.708</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4313</v>
+        <v>0.5724</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2189</v>
+        <v>-1.2804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4487</v>
+        <v>1.8509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5395</v>
+        <v>1.9383</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0907</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5715</v>
+        <v>4.137</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4539</v>
+        <v>1.8037</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1176</v>
+        <v>2.3333</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1227</v>
+        <v>-2.2861</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0856</v>
+        <v>0.1346</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2083</v>
+        <v>-2.4207</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.715</v>
+        <v>-0.4559</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3295</v>
+        <v>-0.4429</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3855</v>
+        <v>-0.013</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.9559</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7154</v>
+        <v>-1.7371</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1712</v>
+        <v>0.7813</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7991</v>
+        <v>0.0555</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0471</v>
+        <v>0.2539</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.752</v>
+        <v>-0.1984</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.358</v>
+        <v>-0.5812</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4184</v>
+        <v>-0.0236</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0604</v>
+        <v>-0.5576</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4411</v>
+        <v>0.6367</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3713</v>
+        <v>0.2775</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8124</v>
+        <v>0.3592</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7055</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7055</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3744</v>
+        <v>-1.9895</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6425</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2681</v>
+        <v>-1.2904</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4036</v>
+        <v>-1.151</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0939</v>
+        <v>-0.5024</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3097</v>
+        <v>-0.6486</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8509</v>
+        <v>0.9356</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9383</v>
+        <v>-1.3307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08740000000000001</v>
+        <v>2.2664</v>
       </c>
       <c r="J6" t="n">
-        <v>4.137</v>
+        <v>0.7357</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8037</v>
+        <v>-1.8449</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3333</v>
+        <v>2.5807</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2861</v>
+        <v>0.1999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1346</v>
+        <v>0.5142</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4207</v>
+        <v>-0.3143</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>2.7055</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1515</v>
+        <v>-1.1866</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1091</v>
+        <v>-0.1976</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0424</v>
+        <v>-0.989</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.23</v>
+        <v>-2.565</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4246</v>
+        <v>-1.2032</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1472</v>
+        <v>0.1332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7225</v>
+        <v>-1.3364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0555</v>
+        <v>0.4487</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2539</v>
+        <v>1.5395</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1984</v>
+        <v>-1.0907</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5812</v>
+        <v>1.5715</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0236</v>
+        <v>1.4539</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5576</v>
+        <v>0.1176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6367</v>
+        <v>-1.1227</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2775</v>
+        <v>0.0856</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3592</v>
+        <v>-1.2083</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4583</v>
+        <v>-1.1306</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1091</v>
+        <v>-0.6277</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3491</v>
+        <v>-0.503</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3538</v>
+        <v>-0.9376</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4363</v>
+        <v>-1.4475</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3767</v>
+        <v>-1.3351</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0596</v>
+        <v>-0.1125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9356</v>
+        <v>-2.7991</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3307</v>
+        <v>-1.0471</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2664</v>
+        <v>-1.752</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7357</v>
+        <v>-1.358</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8449</v>
+        <v>-1.4184</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5807</v>
+        <v>0.0604</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1999</v>
+        <v>-1.4411</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5142</v>
+        <v>0.3713</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3143</v>
+        <v>-1.8124</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6649</v>
+        <v>2.7055</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>2.7055</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4719</v>
+        <v>-0.1864</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0718</v>
+        <v>0.0229</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4</v>
+        <v>-0.2094</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.565</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5665</v>
+        <v>-1.5578</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4164</v>
+        <v>-1.2021</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1501</v>
+        <v>-0.3556</v>
       </c>
       <c r="G9" t="n">
         <v>-2.082</v>
@@ -1156,13 +1156,13 @@
         <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3073</v>
+        <v>0.3161</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1491</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3725</v>
+        <v>0.167</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3499</v>
+        <v>-4.0675</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9951</v>
+        <v>-2.4779</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3548</v>
+        <v>-1.5897</v>
       </c>
       <c r="G10" t="n">
         <v>0.7788</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3367</v>
+        <v>-1.0544</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9134</v>
+        <v>-0.3962</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4233</v>
+        <v>-0.6582</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3351</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9594</v>
+        <v>-4.3351</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2115</v>
+        <v>-1.5872</v>
       </c>
       <c r="F11" t="n">
         <v>-2.7479</v>
@@ -1312,10 +1312,10 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7021</v>
+        <v>-1.0778</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1091</v>
+        <v>-0.4848</v>
       </c>
       <c r="U11" t="n">
         <v>-0.593</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.2289</v>
+        <v>-11.9241</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8351</v>
+        <v>-5.5302</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.3939</v>
+        <v>-6.394</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6936</v>
@@ -1360,7 +1360,7 @@
         <v>4.0828</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.776299999999999</v>
+        <v>-6.7763</v>
       </c>
       <c r="J12" t="n">
         <v>5.369699999999999</v>
@@ -1378,7 +1378,7 @@
         <v>1.3458</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.409299999999998</v>
+        <v>-9.4093</v>
       </c>
       <c r="P12" t="n">
         <v>4.162199999999999</v>
@@ -1390,16 +1390,16 @@
         <v>16.6492</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.6915</v>
+        <v>-8.386700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.7237</v>
+        <v>-3.4192</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.9676</v>
+        <v>-4.9677</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.006300000000001</v>
+        <v>-5.0063</v>
       </c>
       <c r="W12" t="n">
         <v>5.0063</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3556</v>
+        <v>10.4906</v>
       </c>
       <c r="E13" t="n">
-        <v>8.146599999999999</v>
+        <v>8.575200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.209</v>
+        <v>1.9154</v>
       </c>
       <c r="G13" t="n">
         <v>4.2803</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2397</v>
+        <v>2.3748</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6706</v>
+        <v>1.0992</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5691</v>
+        <v>1.2755</v>
       </c>
       <c r="V13" t="n">
         <v>2.795</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.768599999999999</v>
+        <v>9.060700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9823</v>
+        <v>6.3037</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7863</v>
+        <v>2.757</v>
       </c>
       <c r="G14" t="n">
         <v>2.5177</v>
@@ -1546,13 +1546,13 @@
         <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4371</v>
+        <v>0.7292</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3295</v>
+        <v>-0.008</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7373</v>
       </c>
       <c r="V14" t="n">
         <v>3.7325</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3922</v>
+        <v>2.5302</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5608</v>
+        <v>3.3464</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1686</v>
+        <v>-0.8162</v>
       </c>
       <c r="G15" t="n">
         <v>2.5109</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6108</v>
+        <v>1.7488</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2421</v>
+        <v>1.0278</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3687</v>
+        <v>0.721</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5213</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2239</v>
+        <v>0.4405</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5921</v>
+        <v>-1.7318</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6319</v>
+        <v>2.1723</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5416</v>
+        <v>-0.2652</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3775</v>
+        <v>1.9637</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1641</v>
+        <v>-2.2288</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2027</v>
+        <v>0.1555</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3202</v>
+        <v>1.6414</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1176</v>
+        <v>-1.4859</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.339</v>
+        <v>-0.4206</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0573</v>
+        <v>0.3223</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2817</v>
+        <v>-0.7429</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4568</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2224</v>
+        <v>0.5599</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4784</v>
+        <v>0.1939</v>
       </c>
       <c r="U16" t="n">
-        <v>1.744</v>
+        <v>0.3661</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3975</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3039</v>
+        <v>0.0866</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.839</v>
+        <v>0.3062</v>
       </c>
       <c r="F17" t="n">
-        <v>2.143</v>
+        <v>-0.2195</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2652</v>
+        <v>-0.5416</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9637</v>
+        <v>-0.3775</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2288</v>
+        <v>-0.1641</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1555</v>
+        <v>-0.2027</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6414</v>
+        <v>-0.3202</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4859</v>
+        <v>0.1176</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4206</v>
+        <v>-0.339</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3223</v>
+        <v>-0.0573</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7429</v>
+        <v>-0.2817</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4234</v>
+        <v>2.0851</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0867</v>
+        <v>1.1926</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3367</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3538</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5396</v>
+        <v>-0.0611</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8257</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2861</v>
+        <v>0.5503</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3119</v>
@@ -1858,13 +1858,13 @@
         <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6439</v>
+        <v>-0.1654</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1872</v>
+        <v>0.077</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4942</v>
+        <v>-1.4328</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.09</v>
+        <v>-0.538</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4042</v>
+        <v>-0.8948</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3404</v>
+        <v>-2.3734</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3241</v>
+        <v>-0.9765</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0163</v>
+        <v>-1.3969</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2136</v>
+        <v>-1.361</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4096</v>
+        <v>-1.352</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1959</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1268</v>
+        <v>-1.0124</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9145</v>
+        <v>0.3755</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2123</v>
+        <v>-1.3879</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5736</v>
+        <v>0.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0373</v>
+        <v>0.823</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5363</v>
+        <v>0.077</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9376</v>
+        <v>-0.5838</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9114</v>
+        <v>-2.4792</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7523</v>
+        <v>-1.8401</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1591</v>
+        <v>-0.6391</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3734</v>
+        <v>-2.3404</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9765</v>
+        <v>-2.3241</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3969</v>
+        <v>-0.0163</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.361</v>
+        <v>-1.2136</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.352</v>
+        <v>-1.4096</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.1959</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0124</v>
+        <v>-1.1268</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3755</v>
+        <v>-0.9145</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3879</v>
+        <v>-0.2123</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6244</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4214</v>
+        <v>0.5886</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6087</v>
+        <v>0.2872</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1872</v>
+        <v>0.3014</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5838</v>
+        <v>0.9376</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0916</v>
+        <v>-2.6233</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5114</v>
+        <v>-2.1899</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5802</v>
+        <v>-0.4334</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4537</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5141</v>
+        <v>-0.0458</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3138</v>
+        <v>0.0076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2003</v>
+        <v>-0.0535</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7785</v>
+        <v>-2.7832</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7019</v>
+        <v>-4.0589</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9234</v>
+        <v>1.2757</v>
       </c>
       <c r="G22" t="n">
         <v>0.671</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.079</v>
+        <v>0.9163</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0562</v>
+        <v>0.5868</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0228</v>
+        <v>0.3295</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>13.2289</v>
+        <v>13.229</v>
       </c>
       <c r="E23" t="n">
-        <v>7.561500000000001</v>
+        <v>7.561400000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>5.667600000000001</v>
+        <v>5.6677</v>
       </c>
       <c r="G23" t="n">
-        <v>2.693700000000001</v>
+        <v>2.6937</v>
       </c>
       <c r="H23" t="n">
         <v>-4.0826</v>
@@ -2227,7 +2227,7 @@
         <v>-1.3458</v>
       </c>
       <c r="L23" t="n">
-        <v>9.409099999999999</v>
+        <v>9.4091</v>
       </c>
       <c r="M23" t="n">
         <v>-5.3697</v>
@@ -2248,22 +2248,22 @@
         <v>12.4873</v>
       </c>
       <c r="S23" t="n">
-        <v>9.691400000000002</v>
+        <v>9.6915</v>
       </c>
       <c r="T23" t="n">
-        <v>4.967600000000001</v>
+        <v>4.967700000000001</v>
       </c>
       <c r="U23" t="n">
         <v>4.7239</v>
       </c>
       <c r="V23" t="n">
-        <v>5.0062</v>
+        <v>5.006199999999999</v>
       </c>
       <c r="W23" t="n">
         <v>11.1799</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.173800000000001</v>
+        <v>-6.1738</v>
       </c>
     </row>
   </sheetData>
